--- a/stories/arbres/TREE-COL-024.xlsx
+++ b/stories/arbres/TREE-COL-024.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Nora est avec maman, à la maison. Nora a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora écoute maman. Nora entend les mots : écouter, si malaise raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Nora va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nora va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Nora va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nora va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Nora va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-024.xlsx
+++ b/stories/arbres/TREE-COL-024.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Nora est avec maman, à la maison. Nora a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora écoute maman. Nora entend les mots : écouter, si malaise raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Nora a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Nora rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Nora rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Nora rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Nora a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Nora rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Nora rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Nora rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Nora a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Nora rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Nora rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Nora a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Nora rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Nora rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Nora rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Nora a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Nora rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Nora rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Nora a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Nora rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Nora rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Nora rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Nora a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Nora rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Nora rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Nora a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Nora rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Nora rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Nora rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Nora a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Nora rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Nora rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-024.xlsx
+++ b/stories/arbres/TREE-COL-024.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — à la maison</t>
+          <t>Le rond sur la vitre de Nina</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La vitre est embuée. Nina voit le parc. À l'école, elle a écouté la maîtresse. Un camarade a chuchoté. Son ventre s'est serré. Au parc, puis à la maison, elle raconte à papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Nora est avec maman, à la maison. Nora a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora écoute maman. Nora entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>La vitre de la cuisine est toute embuée. La soupe fume encore, près du four. Nina dessine un rond avec le doigt. À travers le rond, le parc brille. Un toboggan gris luit, tout loin. Le manteau goutte encore, sur le crochet. Le cartable est sur la chaise, un peu lourd. Un crayon jaune dépasse, tout lisse. Les chaussures ont encore du sable. Maman essuie la table, tout lentement. Papa range une cuillère dans le tiroir. L'école est finie, Nina. Tu as écouté la maîtresse ? Oui, maman. On t'écoute, ce soir. En ce moment, Nina a le ventre un peu serré. Elle revoit la classe, tout nette. Un camarade a chuchoté, tout près. J'ai un malaise. Tu nous racontes, d'accord ? D'accord. D'abord, on peut aller au parc. Le parc est derrière la haie. Le rond sur la vitre sèche, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,37 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Nora est avec maman, à la maison. Nora a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora écoute maman. Nora entend les mots : écouter, si malaise raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est toute embuée.
+narrateur|La soupe fume encore, près du four.
+narrateur|Nina dessine un rond avec le doigt.
+narrateur|À travers le rond, le parc brille.
+narrateur|Un toboggan gris luit, tout loin.
+narrateur|Le manteau goutte encore, sur le crochet.
+narrateur|Le cartable est sur la chaise, un peu lourd.
+narrateur|Un crayon jaune dépasse, tout lisse.
+narrateur|Les chaussures ont encore du sable.
+narrateur|Maman essuie la table, tout lentement.
+narrateur|Papa range une cuillère dans le tiroir.
+maman|L'école est finie, Nina.
+maman|Tu as écouté la maîtresse ?
+enfant-f|Oui, maman.
+papa|On t'écoute, ce soir.
+narrateur|En ce moment, Nina a le ventre un peu serré.
+narrateur|Elle revoit la classe, tout nette.
+narrateur|Un camarade a chuchoté, tout près.
+enfant-f|J'ai un malaise.
+maman|Tu nous racontes, d'accord ?
+enfant-f|D'accord.
+papa|D'abord, on peut aller au parc.
+papa|Le parc est derrière la haie.
+narrateur|Le rond sur la vitre sèche, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1392,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Le parc est tout près, derrière la haie. Le bac à sable, le toboggan, ou les balançoires ? On écoute. Ensuite, si malaise, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,10 +1556,17 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le parc est tout près, derrière la haie.
+maman|Le bac à sable, le toboggan, ou les balançoires ?
+papa|On écoute.
+papa|Ensuite, si malaise, on raconte à la maison.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1545,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nora va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Nina s'agenouille près du bac à sable. Le sable est tiède, un peu rêche. Un grain colle à son genou. Elle se souvient de la classe. La maîtresse parlait, tout près du tableau. On écoute, ensemble. Nina a écouté. Un camarade a chuchoté, tout près. Son ventre s'est serré, tout petit. Elle est restée près du sable, maintenant. J'ai écouté la maîtresse. J'ai un malaise. Tu racontes à la maison. Papa et maman t'écoutent. Bravo, Nina. Tu as écouté. Ensuite, tu racontes. Nina laisse le sable glisser entre ses doigts.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1731,31 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nora va vers le bac à sable. La lumière est claire. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina s'agenouille près du bac à sable.
+narrateur|Le sable est tiède, un peu rêche.
+narrateur|Un grain colle à son genou.
+narrateur|Elle se souvient de la classe.
+narrateur|La maîtresse parlait, tout près du tableau.
+maitresse|On écoute, ensemble.
+narrateur|Nina a écouté.
+narrateur|Un camarade a chuchoté, tout près.
+narrateur|Son ventre s'est serré, tout petit.
+narrateur|Elle est restée près du sable, maintenant.
+enfant-f|J'ai écouté la maîtresse.
+enfant-f|J'ai un malaise.
+maman|Tu racontes à la maison.
+maman|Papa et maman t'écoutent.
+papa|Bravo, Nina.
+papa|Tu as écouté.
+papa|Ensuite, tu racontes.
+narrateur|Nina laisse le sable glisser entre ses doigts.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nina a un malaise. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1940,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nina a un malaise.
+maman|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina souffle. Un grain de sable reste sur son genou. Je raconte à papa, ou à maman. On t'écoute. Bravo, Nina. Le ventre se desserre un tout petit peu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2113,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+narrateur|Nina souffle.
+narrateur|Un grain de sable reste sur son genou.
+enfant-f|Je raconte à papa, ou à maman.
+papa|On t'écoute.
+papa|Bravo, Nina.
+narrateur|Le ventre se desserre un tout petit peu.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2149,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, tout proches. Le ballon, le seau, ou le doudou ? On joue. Ensuite, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2313,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, tout proches.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|Ensuite, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2344,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nina prend le ballon. Le ballon est un peu sablé. Il fait poum contre le sol. Tu veux le ballon ? Oui. S'il te plaît. Tiens. Merci, papa. Tu as écouté, à l'école. Si malaise, tu racontes à la maison. Nina serre le ballon contre son ventre. Mon ventre est encore un peu serré. On t'écoute. Le ballon a une tache de sable, toute fine. On est encore près de le bac à sable. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2484,30 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon.
+narrateur|Le ballon est un peu sablé.
+narrateur|Il fait poum contre le sol.
+papa|Tu veux le ballon ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+papa|Tiens.
+enfant-f|Merci, papa.
+maman|Tu as écouté, à l'école.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Nina serre le ballon contre son ventre.
+enfant-f|Mon ventre est encore un peu serré.
+papa|On t'écoute.
+narrateur|Le ballon a une tache de sable, toute fine.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2532,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2700,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2731,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom a du sable sur le ventre. Nina a encore le ballon, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,7 +2871,32 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. On entend un oiseau. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom a du sable sur le ventre.
+narrateur|Nina a encore le ballon, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2798,7 +2924,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le ballon. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3064,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3100,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa a un grain de sable au bouton. Nina a encore le ballon, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,7 +3240,32 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa a un grain de sable au bouton.
+narrateur|Nina a encore le ballon, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3134,7 +3293,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le ballon. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3433,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3469,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami a du sable dans la crinière. Nina a encore le ballon, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,7 +3609,31 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami a du sable dans la crinière.
+narrateur|Nina a encore le ballon, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3470,7 +3661,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le ballon. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3801,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3837,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Nina prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Tu verses, tout doux ? S'il te plaît. Oui. Merci, maman. À l'école, on écoute la maîtresse. Ensuite, si malaise, on raconte à la maison. Nina pose le seau près de ses genoux. J'ai écouté. Bravo. Tu nous racontes. Le seau laisse un rond mouillé dans le sable. On est encore près de le bac à sable. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,10 +3977,30 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Tu verses, tout doux ?
+enfant-f|S'il te plaît.
+maman|Oui.
+enfant-f|Merci, maman.
+papa|À l'école, on écoute la maîtresse.
+papa|Ensuite, si malaise, on raconte à la maison.
+narrateur|Nina pose le seau près de ses genoux.
+enfant-f|J'ai écouté.
+maman|Bravo.
+maman|Tu nous racontes.
+narrateur|Le seau laisse un rond mouillé dans le sable.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3806,7 +4025,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4193,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4224,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom regarde l'eau du seau, tout calme. Nina a encore le seau, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,7 +4364,32 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom regarde l'eau du seau, tout calme.
+narrateur|Nina a encore le seau, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4170,7 +4417,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le seau. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4557,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4593,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa a une goutte sur la robe. Nina a encore le seau, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,7 +4733,32 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Le vent est doux. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa a une goutte sur la robe.
+narrateur|Nina a encore le seau, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4506,7 +4786,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le seau. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4926,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4962,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami lape une goutte, tout doux. Nina a encore le seau, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,7 +5102,31 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami lape une goutte, tout doux.
+narrateur|Nina a encore le seau, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4842,7 +5154,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le seau. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5294,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5330,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+          <t>Nina prend le doudou. Le doudou est gris, un peu sablé. Une oreille est encore chaude. Doudou, j'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. Tu as écouté la maîtresse. Ensuite, tu racontes. Merci, papa. Merci, maman. Nina serre le doudou, tout doux. Bravo, Nina. Un grain de sable colle à l'oreille du doudou. On est encore près de le bac à sable. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,7 +5470,22 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Le doudou est gris, un peu sablé.
+narrateur|Une oreille est encore chaude.
+enfant-f|Doudou, j'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|Tu as écouté la maîtresse.
+papa|Ensuite, tu racontes.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Nina serre le doudou, tout doux.
+maman|Bravo, Nina.
+narrateur|Un grain de sable colle à l'oreille du doudou.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5178,7 +5513,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,7 +5681,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5374,7 +5712,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom se colle au doudou gris. Nina a encore le doudou, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,7 +5852,32 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Le vent est doux. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom se colle au doudou gris.
+narrateur|Nina a encore le doudou, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5542,7 +5905,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le doudou. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,7 +6045,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5710,7 +6081,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa s'assoit près du doudou. Nina a encore le doudou, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,7 +6221,32 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa s'assoit près du doudou.
+narrateur|Nina a encore le doudou, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5878,7 +6274,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le doudou. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,7 +6414,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6046,7 +6450,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami pose la tête sur le doudou. Nina a encore le doudou, près de le bac à sable. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,7 +6590,31 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le bac à sable, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami pose la tête sur le doudou.
+narrateur|Nina a encore le doudou, près de le bac à sable.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6214,7 +6642,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le bac à sable. Elle a tenu le doudou. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,7 +6782,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le bac à sable.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6382,7 +6818,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nora va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Nina pose la main sur le toboggan. Le métal est un peu froid. Une marche sonne, tout creux. Elle revoit la classe, tout nette. La maîtresse ouvrait un livre. On écoute d'abord. Nina a écouté jusqu'au bout. Un camarade a parlé tout bas. Nina a senti un malaise. Ses mains sont devenues chaudes. Mon ventre s'est serré. Tu as écouté la maîtresse. Si malaise, tu racontes à la maison. On t'écoute, Nina. C'est du bon travail. Nina reste en bas du toboggan, tout calme. Je raconte à papa, ou à maman.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,11 +6958,30 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Nora va vers le toboggan. Il y a des miettes sur la table. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina pose la main sur le toboggan.
+narrateur|Le métal est un peu froid.
+narrateur|Une marche sonne, tout creux.
+narrateur|Elle revoit la classe, tout nette.
+narrateur|La maîtresse ouvrait un livre.
+maitresse|On écoute d'abord.
+narrateur|Nina a écouté jusqu'au bout.
+narrateur|Un camarade a parlé tout bas.
+narrateur|Nina a senti un malaise.
+narrateur|Ses mains sont devenues chaudes.
+enfant-f|Mon ventre s'est serré.
+maman|Tu as écouté la maîtresse.
+maman|Si malaise, tu racontes à la maison.
+papa|On t'écoute, Nina.
+papa|C'est du bon travail.
+narrateur|Nina reste en bas du toboggan, tout calme.
+enfant-f|Je raconte à papa, ou à maman.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6551,7 +7006,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>À l'école, Nina écoute. Et si malaise, on raconte à la maison ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6711,7 +7166,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|À l'école, Nina écoute.
+papa|Et si malaise, on raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6739,7 +7195,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute. Si malaise, raconter à la maison. Nina essuie ses mains sur son manteau. Le tissu est un peu rêche. J'ai écouté. Et tu nous racontes. C'est du bon travail. Le métal du toboggan reste froid, tout calme.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6883,7 +7339,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|On écoute.
+papa|Si malaise, raconter à la maison.
+narrateur|Nina essuie ses mains sur son manteau.
+narrateur|Le tissu est un peu rêche.
+enfant-f|J'ai écouté.
+maman|Et tu nous racontes.
+maman|C'est du bon travail.
+narrateur|Le métal du toboggan reste froid, tout calme.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6911,7 +7375,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, tout proches. Le ballon, le seau, ou le doudou ? On joue. Ensuite, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7075,7 +7539,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, tout proches.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|Ensuite, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7103,7 +7570,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nina prend le ballon. Le ballon est un peu sablé. Il fait poum contre le sol. Tu veux le ballon ? Oui. S'il te plaît. Tiens. Merci, papa. Tu as écouté, à l'école. Si malaise, tu racontes à la maison. Nina serre le ballon contre son ventre. Mon ventre est encore un peu serré. On t'écoute. Le ballon roule jusqu'à la première marche. On est encore près de le toboggan. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7243,10 +7710,30 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le ballon. On entend un oiseau. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon.
+narrateur|Le ballon est un peu sablé.
+narrateur|Il fait poum contre le sol.
+papa|Tu veux le ballon ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+papa|Tiens.
+enfant-f|Merci, papa.
+maman|Tu as écouté, à l'école.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Nina serre le ballon contre son ventre.
+enfant-f|Mon ventre est encore un peu serré.
+papa|On t'écoute.
+narrateur|Le ballon roule jusqu'à la première marche.
+narrateur|On est encore près de le toboggan.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7758,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,7 +7926,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7467,7 +7957,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom roule un peu, comme le ballon. Nina a encore le ballon, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,7 +8097,32 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom roule un peu, comme le ballon.
+narrateur|Nina a encore le ballon, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7635,7 +8150,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le ballon. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,7 +8290,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7803,7 +8326,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa tient le ballon, trop grand. Nina a encore le ballon, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,7 +8466,32 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa tient le ballon, trop grand.
+narrateur|Nina a encore le ballon, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7971,7 +8519,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le ballon. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,7 +8659,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8139,7 +8695,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami garde le ballon entre les pattes. Nina a encore le ballon, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,7 +8835,31 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le toboggan, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami garde le ballon entre les pattes.
+narrateur|Nina a encore le ballon, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8307,7 +8887,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le ballon. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,7 +9027,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8475,7 +9063,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Nina prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Tu verses, tout doux ? S'il te plaît. Oui. Merci, maman. À l'école, on écoute la maîtresse. Ensuite, si malaise, on raconte à la maison. Nina pose le seau près de ses genoux. J'ai écouté. Bravo. Tu nous racontes. Le seau sonne contre le métal, tout creux. On est encore près de le toboggan. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,10 +9203,30 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le seau. Ça sent le pain chaud. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Tu verses, tout doux ?
+enfant-f|S'il te plaît.
+maman|Oui.
+enfant-f|Merci, maman.
+papa|À l'école, on écoute la maîtresse.
+papa|Ensuite, si malaise, on raconte à la maison.
+narrateur|Nina pose le seau près de ses genoux.
+enfant-f|J'ai écouté.
+maman|Bravo.
+maman|Tu nous racontes.
+narrateur|Le seau sonne contre le métal, tout creux.
+narrateur|On est encore près de le toboggan.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8643,7 +9251,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,7 +9419,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8839,7 +9450,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom a l'oreille mouillée, près du seau. Nina a encore le seau, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,7 +9590,32 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Le vent est doux. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom a l'oreille mouillée, près du seau.
+narrateur|Nina a encore le seau, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9007,7 +9643,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le seau. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,7 +9783,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9175,7 +9819,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa a un ticket de papier dans le seau. Nina a encore le seau, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,7 +9959,32 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa a un ticket de papier dans le seau.
+narrateur|Nina a encore le seau, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9343,7 +10012,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le seau. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,7 +10152,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9511,7 +10188,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami écoute le seau, tout creux. Nina a encore le seau, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,7 +10328,31 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Une feuille tombe. On attend son tour. Cette fin-là est celle de le toboggan, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami écoute le seau, tout creux.
+narrateur|Nina a encore le seau, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9679,7 +10380,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le seau. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,7 +10520,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9847,7 +10556,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+          <t>Nina prend le doudou. Le doudou est gris, un peu sablé. Une oreille est encore chaude. Doudou, j'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. Tu as écouté la maîtresse. Ensuite, tu racontes. Merci, papa. Merci, maman. Nina serre le doudou, tout doux. Bravo, Nina. Le doudou s'assoit en bas du toboggan. On est encore près de le toboggan. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,7 +10696,22 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le doudou. Le vent est doux. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Le doudou est gris, un peu sablé.
+narrateur|Une oreille est encore chaude.
+enfant-f|Doudou, j'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|Tu as écouté la maîtresse.
+papa|Ensuite, tu racontes.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Nina serre le doudou, tout doux.
+maman|Bravo, Nina.
+narrateur|Le doudou s'assoit en bas du toboggan.
+narrateur|On est encore près de le toboggan.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10015,7 +10739,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,7 +10907,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10211,7 +10938,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom s'assoit en bas, près du doudou. Nina a encore le doudou, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,7 +11078,32 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom s'assoit en bas, près du doudou.
+narrateur|Nina a encore le doudou, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10379,7 +11131,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le doudou. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,7 +11271,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10547,7 +11307,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa a la robe froissée, comme le doudou. Nina a encore le doudou, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,7 +11447,32 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa a la robe froissée, comme le doudou.
+narrateur|Nina a encore le doudou, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10715,7 +11500,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le doudou. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,7 +11640,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10883,7 +11676,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami chauffe contre le doudou. Nina a encore le doudou, près de le toboggan. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,7 +11816,31 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le toboggan, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami chauffe contre le doudou.
+narrateur|Nina a encore le doudou, près de le toboggan.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11051,7 +11868,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de le toboggan. Elle a tenu le doudou. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,7 +12008,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de le toboggan.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11219,7 +12044,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Nora va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Nina s'assoit sur la balançoire. La chaîne est froide, un peu rêche. Elle fait un tout petit criiiii. Nina pense à l'école, encore. La maîtresse disait les mots, tout doux. Merci d'avoir écouté. Nina a écouté. Le malaise est resté, tout petit. Un camarade a chuchoté près de l'oreille. J'ai un malaise, maman. Tu as bien fait de le dire. On écoute la maîtresse. Si malaise, on raconte à la maison. Je t'écoute, Nina. Bravo. La balançoire s'arrête, tout doucement.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,11 +12184,29 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Nora va vers les balançoires. Un chat miaule une fois. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Nora se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On écoute jusqu'au bout.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Nina s'assoit sur la balançoire.
+narrateur|La chaîne est froide, un peu rêche.
+narrateur|Elle fait un tout petit criiiii.
+narrateur|Nina pense à l'école, encore.
+narrateur|La maîtresse disait les mots, tout doux.
+maitresse|Merci d'avoir écouté.
+narrateur|Nina a écouté.
+narrateur|Le malaise est resté, tout petit.
+narrateur|Un camarade a chuchoté près de l'oreille.
+enfant-f|J'ai un malaise, maman.
+maman|Tu as bien fait de le dire.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Je t'écoute, Nina.
+papa|Bravo.
+narrateur|La balançoire s'arrête, tout doucement.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11388,7 +12231,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Nina a écouté la maîtresse. On raconte à la maison ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11548,7 +12391,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Nina a écouté la maîtresse.
+maman|On raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11576,7 +12420,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On écoute la maîtresse. Si malaise, raconter à papa ou maman. Nina hoche la tête. La chaîne ne crie plus. J'écoute. Puis je raconte. Bravo. On continue ensemble.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11720,7 +12564,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora respire. Nora retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à papa ou maman.
+narrateur|Nina hoche la tête.
+narrateur|La chaîne ne crie plus.
+enfant-f|J'écoute.
+enfant-f|Puis je raconte.
+papa|Bravo.
+papa|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11748,7 +12600,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, tout proches. Le ballon, le seau, ou le doudou ? On joue. Ensuite, on raconte à la maison.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11912,7 +12764,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, tout proches.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|Ensuite, on raconte à la maison.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11940,7 +12795,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Nina prend le ballon. Le ballon est un peu sablé. Il fait poum contre le sol. Tu veux le ballon ? Oui. S'il te plaît. Tiens. Merci, papa. Tu as écouté, à l'école. Si malaise, tu racontes à la maison. Nina serre le ballon contre son ventre. Mon ventre est encore un peu serré. On t'écoute. Le ballon attend sous la balançoire, tout sage. On est encore près de les balançoires. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12080,10 +12935,30 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nina prend le ballon.
+narrateur|Le ballon est un peu sablé.
+narrateur|Il fait poum contre le sol.
+papa|Tu veux le ballon ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+papa|Tiens.
+enfant-f|Merci, papa.
+maman|Tu as écouté, à l'école.
+maman|Si malaise, tu racontes à la maison.
+narrateur|Nina serre le ballon contre son ventre.
+enfant-f|Mon ventre est encore un peu serré.
+papa|On t'écoute.
+narrateur|Le ballon attend sous la balançoire, tout sage.
+narrateur|On est encore près de les balançoires.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12108,7 +12983,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12276,7 +13151,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12304,7 +13182,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom attend sous la balançoire, près du ballon. Nina a encore le ballon, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12444,7 +13322,32 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom attend sous la balançoire, près du ballon.
+narrateur|Nina a encore le ballon, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12472,7 +13375,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le ballon. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12612,7 +13515,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12640,7 +13551,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa a le ballon sur les genoux. Nina a encore le ballon, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12780,7 +13691,32 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa a le ballon sur les genoux.
+narrateur|Nina a encore le ballon, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12808,7 +13744,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le ballon. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12948,7 +13884,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12976,7 +13920,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami suit le ballon des yeux. Nina a encore le ballon, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13116,7 +14060,31 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le ballon et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami suit le ballon des yeux.
+narrateur|Nina a encore le ballon, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13144,7 +14112,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le ballon. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13284,7 +14252,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le ballon.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13312,7 +14288,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Nina prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Tu verses, tout doux ? S'il te plaît. Oui. Merci, maman. À l'école, on écoute la maîtresse. Ensuite, si malaise, on raconte à la maison. Nina pose le seau près de ses genoux. J'ai écouté. Bravo. Tu nous racontes. Le seau tremble un peu, près de la chaîne. On est encore près de les balançoires. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13452,10 +14428,30 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nina prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Tu verses, tout doux ?
+enfant-f|S'il te plaît.
+maman|Oui.
+enfant-f|Merci, maman.
+papa|À l'école, on écoute la maîtresse.
+papa|Ensuite, si malaise, on raconte à la maison.
+narrateur|Nina pose le seau près de ses genoux.
+enfant-f|J'ai écouté.
+maman|Bravo.
+maman|Tu nous racontes.
+narrateur|Le seau tremble un peu, près de la chaîne.
+narrateur|On est encore près de les balançoires.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13480,7 +14476,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13648,7 +14644,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13676,7 +14675,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom a une goutte sur le nez, près du seau. Nina a encore le seau, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13816,7 +14815,32 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom a une goutte sur le nez, près du seau.
+narrateur|Nina a encore le seau, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13844,7 +14868,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le seau. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13984,7 +15008,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14012,7 +15044,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa tient le seau, trop lourd. Nina a encore le seau, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14152,7 +15184,32 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. Une feuille tombe. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa tient le seau, trop lourd.
+narrateur|Nina a encore le seau, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14180,7 +15237,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le seau. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14320,7 +15377,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14348,7 +15413,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami a la crinière mouillée, un peu. Nina a encore le seau, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14488,7 +15553,31 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le seau et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami a la crinière mouillée, un peu.
+narrateur|Nina a encore le seau, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14516,7 +15605,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le seau. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14656,7 +15745,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le seau.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14684,7 +15781,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Nora a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+          <t>Nina prend le doudou. Le doudou est gris, un peu sablé. Une oreille est encore chaude. Doudou, j'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. Tu as écouté la maîtresse. Ensuite, tu racontes. Merci, papa. Merci, maman. Nina serre le doudou, tout doux. Bravo, Nina. Le doudou a une place, sur les genoux. On est encore près de les balançoires. On écoute la maîtresse. Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14824,7 +15921,22 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Nora a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora répète tout bas : écouter, si malaise raconter à la maison. On rit un peu. papa n'est pas loin.</t>
+          <t>narrateur|Nina prend le doudou.
+narrateur|Le doudou est gris, un peu sablé.
+narrateur|Une oreille est encore chaude.
+enfant-f|Doudou, j'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|Tu as écouté la maîtresse.
+papa|Ensuite, tu racontes.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Nina serre le doudou, tout doux.
+maman|Bravo, Nina.
+narrateur|Le doudou a une place, sur les genoux.
+narrateur|On est encore près de les balançoires.
+maman|On écoute la maîtresse.
+maman|Si malaise, raconter à la maison.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14852,7 +15964,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Trois peluches écoutent, tout calmes. Tom, Léa, ou Sami ? Tu t'assoies un peu. Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15020,7 +16132,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Trois peluches écoutent, tout calmes.
+maman|Tom, Léa, ou Sami ?
+papa|Tu t'assoies un peu.
+papa|Ensuite, tu racontes à la maison.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15048,7 +16163,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint l'ours Tom. L'ours est brun, un peu râpé. Une oreille est plus douce que l'autre. Nina l'assoit contre son genou. Tom, j'ai écouté. J'ai un malaise. Tu peux le dire à la maison. Papa et maman t'écoutent. On écoute la maîtresse. Si malaise, on raconte à la maison. Nina caresse l'oreille de l'ours. L'ours Tom et le doudou partagent les genoux. Nina a encore le doudou, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15188,7 +16303,32 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Tom. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Tom. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint l'ours Tom.
+narrateur|L'ours est brun, un peu râpé.
+narrateur|Une oreille est plus douce que l'autre.
+narrateur|Nina l'assoit contre son genou.
+enfant-f|Tom, j'ai écouté.
+enfant-f|J'ai un malaise.
+maman|Tu peux le dire à la maison.
+maman|Papa et maman t'écoutent.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|Nina caresse l'oreille de l'ours.
+narrateur|L'ours Tom et le doudou partagent les genoux.
+narrateur|Nina a encore le doudou, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15216,7 +16356,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le doudou. Elle a parlé près de l'ours Tom. L'ours Tom s'endort contre le genou. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15356,7 +16496,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de l'ours Tom.
+narrateur|L'ours Tom s'endort contre le genou.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15384,7 +16532,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint la poupée Léa. La robe est bleue, un peu froissée. Un bouton brille, tout petit. Nina pose Léa sur ses genoux. Léa, j'ai écouté la maîtresse. Mon ventre est serré. Ce n'est pas un secret pour nous. Tu racontes à la maison. On t'écoute. Nina lisse la robe bleue. Le malaise est encore là, tout petit. La poupée Léa s'endort presque, près du doudou. Nina a encore le doudou, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15524,7 +16672,32 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Léa. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Léa. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint la poupée Léa.
+narrateur|La robe est bleue, un peu froissée.
+narrateur|Un bouton brille, tout petit.
+narrateur|Nina pose Léa sur ses genoux.
+enfant-f|Léa, j'ai écouté la maîtresse.
+enfant-f|Mon ventre est serré.
+maman|Ce n'est pas un secret pour nous.
+maman|Tu racontes à la maison.
+papa|On t'écoute.
+narrateur|Nina lisse la robe bleue.
+narrateur|Le malaise est encore là, tout petit.
+narrateur|La poupée Léa s'endort presque, près du doudou.
+narrateur|Nina a encore le doudou, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15552,7 +16725,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le doudou. Elle a parlé près de la poupée Léa. La poupée Léa garde son bouton brillant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15692,7 +16865,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de la poupée Léa.
+narrateur|La poupée Léa garde son bouton brillant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15720,7 +16901,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Nora rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>Nina rejoint le lion Sami. La crinière est en laine, un peu mêlée. Un œil de bouton regarde, tout calme. Nina tient Sami contre son manteau. Sami, j'ai un malaise. Tu as écouté la maîtresse. Ensuite, tu racontes à papa ou maman. Je t'écoute. Bravo, Nina. Nina range une mèche de laine. Le lion Sami écoute la chaîne, tout calme, près du doudou. Nina a encore le doudou, près de les balançoires. Papa. Maman. J'ai eu un malaise. Un camarade a chuchoté. J'ai écouté la maîtresse. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, on raconte à la maison. Bravo, Nina. C'est du bon travail. Merci, maman. Merci, papa. Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15860,7 +17041,31 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Nora rejoint Sami. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de les balançoires, le doudou et Sami. Nora a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Nora a entendu : écouter, si malaise raconter à la maison. Nora dit merci à maman. On rentre.</t>
+          <t>narrateur|Nina rejoint le lion Sami.
+narrateur|La crinière est en laine, un peu mêlée.
+narrateur|Un œil de bouton regarde, tout calme.
+narrateur|Nina tient Sami contre son manteau.
+enfant-f|Sami, j'ai un malaise.
+maman|Tu as écouté la maîtresse.
+maman|Ensuite, tu racontes à papa ou maman.
+papa|Je t'écoute.
+papa|Bravo, Nina.
+narrateur|Nina range une mèche de laine.
+narrateur|Le lion Sami écoute la chaîne, tout calme, près du doudou.
+narrateur|Nina a encore le doudou, près de les balançoires.
+enfant-f|Papa.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Un camarade a chuchoté.
+enfant-f|J'ai écouté la maîtresse.
+papa|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, on raconte à la maison.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+narrateur|Le ventre de Nina se desserre, tout doucement.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15888,7 +17093,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo, Nina. Tu as fait du bon travail. Nina a joué près de les balançoires. Elle a tenu le doudou. Elle a parlé près de le lion Sami. Le lion Sami a la crinière un peu plus sage. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16028,7 +17233,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|Nina a joué près de les balançoires.
+narrateur|Elle a tenu le doudou.
+narrateur|Elle a parlé près de le lion Sami.
+narrateur|Le lion Sami a la crinière un peu plus sage.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16050,7 +17263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16144,6 +17357,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
